--- a/Assets/StreamingAssets/Config_dung.xlsx
+++ b/Assets/StreamingAssets/Config_dung.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\GG\Jeronimo\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE9C2A9-9D88-4ED3-9AFB-98F452213E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959292E1-44DF-45AA-9ADF-B9AB6CD94E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5921,13 +5921,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="48">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="H7" s="48">
         <v>45</v>
       </c>
       <c r="I7" s="48">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="J7" s="48">
         <v>1</v>
@@ -27534,7 +27534,7 @@
         <v>1516</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" customHeight="1">
